--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -911,7 +911,7 @@
         <v>19</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -1067,7 +1067,7 @@
         <v>292</v>
       </c>
       <c r="P12" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -529,7 +529,7 @@
         <v>356</v>
       </c>
       <c r="J2" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K2" t="n">
         <v>149</v>
@@ -547,7 +547,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -642,10 +642,10 @@
         <v>24</v>
       </c>
       <c r="M4" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N4" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O4" t="n">
         <v>43</v>
@@ -688,7 +688,7 @@
         <v>263</v>
       </c>
       <c r="K5" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L5" t="n">
         <v>100</v>
@@ -703,7 +703,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -737,25 +737,25 @@
         <v>59</v>
       </c>
       <c r="J6" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="K6" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L6" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M6" t="n">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="N6" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O6" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="P6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -771,7 +771,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E7" t="n">
         <v>41</v>
@@ -795,19 +795,19 @@
         <v>204</v>
       </c>
       <c r="L7" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M7" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N7" t="n">
         <v>171</v>
       </c>
       <c r="O7" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -823,7 +823,7 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>19</v>
@@ -832,7 +832,7 @@
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
@@ -841,16 +841,16 @@
         <v>30</v>
       </c>
       <c r="J8" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K8" t="n">
         <v>46</v>
       </c>
       <c r="L8" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M8" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N8" t="n">
         <v>31</v>
@@ -859,7 +859,7 @@
         <v>30</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -875,7 +875,7 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
         <v>12</v>
@@ -884,7 +884,7 @@
         <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H9" t="n">
         <v>10</v>
@@ -911,7 +911,7 @@
         <v>19</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -927,7 +927,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
@@ -945,7 +945,7 @@
         <v>12</v>
       </c>
       <c r="J10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K10" t="n">
         <v>17</v>
@@ -997,7 +997,7 @@
         <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
         <v>8</v>
@@ -1015,7 +1015,7 @@
         <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1067,7 +1067,7 @@
         <v>292</v>
       </c>
       <c r="P12" t="n">
-        <v>97</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -911,7 +911,7 @@
         <v>19</v>
       </c>
       <c r="P9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -963,7 +963,7 @@
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1067,7 +1067,7 @@
         <v>292</v>
       </c>
       <c r="P12" t="n">
-        <v>134</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -911,7 +911,7 @@
         <v>19</v>
       </c>
       <c r="P9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -1067,7 +1067,7 @@
         <v>292</v>
       </c>
       <c r="P12" t="n">
-        <v>194</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -963,7 +963,7 @@
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1067,7 +1067,7 @@
         <v>292</v>
       </c>
       <c r="P12" t="n">
-        <v>212</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -911,7 +911,7 @@
         <v>19</v>
       </c>
       <c r="P9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -1067,7 +1067,7 @@
         <v>292</v>
       </c>
       <c r="P12" t="n">
-        <v>229</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -547,7 +547,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -703,7 +703,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -746,7 +746,7 @@
         <v>86</v>
       </c>
       <c r="M6" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N6" t="n">
         <v>155</v>
@@ -765,13 +765,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E7" t="n">
         <v>41</v>
@@ -789,16 +789,16 @@
         <v>126</v>
       </c>
       <c r="J7" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K7" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L7" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M7" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="N7" t="n">
         <v>171</v>
@@ -823,7 +823,7 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>19</v>
@@ -838,16 +838,16 @@
         <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J8" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K8" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L8" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M8" t="n">
         <v>55</v>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
@@ -890,7 +890,7 @@
         <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J9" t="n">
         <v>30</v>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J10" t="n">
         <v>9</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -1067,7 +1067,7 @@
         <v>292</v>
       </c>
       <c r="P12" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -547,7 +547,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
@@ -859,7 +859,7 @@
         <v>30</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -963,7 +963,7 @@
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1067,7 +1067,7 @@
         <v>292</v>
       </c>
       <c r="P12" t="n">
-        <v>250</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -547,7 +547,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
@@ -703,7 +703,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -749,13 +749,13 @@
         <v>212</v>
       </c>
       <c r="N6" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O6" t="n">
         <v>89</v>
       </c>
       <c r="P6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -807,7 +807,7 @@
         <v>180</v>
       </c>
       <c r="P7" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
@@ -859,7 +859,7 @@
         <v>30</v>
       </c>
       <c r="P8" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -911,7 +911,7 @@
         <v>19</v>
       </c>
       <c r="P9" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -1061,13 +1061,13 @@
         <v>62</v>
       </c>
       <c r="N12" t="n">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="O12" t="n">
         <v>292</v>
       </c>
       <c r="P12" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -547,7 +547,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
@@ -911,7 +911,7 @@
         <v>19</v>
       </c>
       <c r="P9" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -1067,7 +1067,7 @@
         <v>292</v>
       </c>
       <c r="P12" t="n">
-        <v>265</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -547,7 +547,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -1067,7 +1067,7 @@
         <v>292</v>
       </c>
       <c r="P12" t="n">
-        <v>288</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -697,13 +697,13 @@
         <v>320</v>
       </c>
       <c r="N5" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O5" t="n">
         <v>82</v>
       </c>
       <c r="P5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -722,7 +722,7 @@
         <v>22</v>
       </c>
       <c r="E6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
         <v>26</v>
@@ -755,7 +755,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -774,7 +774,7 @@
         <v>55</v>
       </c>
       <c r="E7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F7" t="n">
         <v>35</v>
@@ -789,7 +789,7 @@
         <v>126</v>
       </c>
       <c r="J7" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K7" t="n">
         <v>203</v>
@@ -801,13 +801,13 @@
         <v>329</v>
       </c>
       <c r="N7" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O7" t="n">
         <v>180</v>
       </c>
       <c r="P7" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8">
@@ -841,13 +841,13 @@
         <v>29</v>
       </c>
       <c r="J8" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K8" t="n">
         <v>47</v>
       </c>
       <c r="L8" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M8" t="n">
         <v>55</v>
@@ -859,7 +859,7 @@
         <v>30</v>
       </c>
       <c r="P8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -899,7 +899,7 @@
         <v>43</v>
       </c>
       <c r="L9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M9" t="n">
         <v>34</v>
@@ -908,10 +908,10 @@
         <v>28</v>
       </c>
       <c r="O9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P9" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -960,10 +960,10 @@
         <v>8</v>
       </c>
       <c r="O10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P10" t="n">
         <v>4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1067,7 +1067,7 @@
         <v>292</v>
       </c>
       <c r="P12" t="n">
-        <v>312</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -1,40 +1,135 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+  <si>
+    <t>GMV slab</t>
+  </si>
+  <si>
+    <t>2025-07</t>
+  </si>
+  <si>
+    <t>2025-08</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>2025-11</t>
+  </si>
+  <si>
+    <t>2025-12</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+  <si>
+    <t>£0-£50</t>
+  </si>
+  <si>
+    <t>£50-£100</t>
+  </si>
+  <si>
+    <t>£100-£200</t>
+  </si>
+  <si>
+    <t>£200-£500</t>
+  </si>
+  <si>
+    <t>£500-£1K</t>
+  </si>
+  <si>
+    <t>£1K-£5K</t>
+  </si>
+  <si>
+    <t>£5K-£10K</t>
+  </si>
+  <si>
+    <t>£10K-£25K</t>
+  </si>
+  <si>
+    <t>£25K-£50K</t>
+  </si>
+  <si>
+    <t>£50K+</t>
+  </si>
+  <si>
+    <t>No data</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +137,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,669 +454,647 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:P12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>GMV slab</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
+    <row r="1" spans="1:17">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="2" spans="1:17">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
         <v>15</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>12</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>245</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>394</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>459</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>294</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>615</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>356</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>394</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>149</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>40</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>1556</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>979</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2">
         <v>86</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2">
         <v>54</v>
       </c>
+      <c r="Q2">
+        <v>2</v>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>£50-£100</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:17">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>4</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>22</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>12</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>21</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>18</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>37</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>49</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>132</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>63</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>20</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>192</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>83</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3">
         <v>17</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3">
         <v>3</v>
       </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>£100-£200</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:17">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>18</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>21</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>36</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>22</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>45</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>54</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>169</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>83</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>24</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>248</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>160</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4">
         <v>43</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4">
         <v>8</v>
       </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>£200-£500</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:17">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
         <v>7</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>7</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>40</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>30</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>15</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>25</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>40</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>87</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>263</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>142</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>100</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>320</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5">
         <v>217</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5">
         <v>82</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5">
         <v>13</v>
       </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>£500-£1K</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:17">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6">
         <v>7</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>3</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>22</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>20</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>26</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>14</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>22</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>59</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>173</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>117</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>86</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>212</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>156</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6">
         <v>89</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6">
         <v>21</v>
       </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>£1K-£5K</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:17">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7">
         <v>16</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>55</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>42</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>35</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>28</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>27</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>126</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>254</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>203</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>198</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>329</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7">
         <v>172</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7">
         <v>180</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7">
         <v>69</v>
       </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:17">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8">
         <v>6</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>2</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>9</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>19</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>6</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>9</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>5</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>29</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>49</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>47</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>50</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>55</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8">
         <v>31</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8">
         <v>30</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8">
         <v>16</v>
       </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>£10K-£25K</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:17">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
         <v>10</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>2</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>13</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>12</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>9</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>12</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>10</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>35</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>30</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>43</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>33</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>34</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9">
         <v>28</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9">
         <v>18</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9">
         <v>33</v>
       </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>£25K-£50K</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:17">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10">
         <v>3</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>0</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>2</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>9</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>8</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>2</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>2</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>14</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>9</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>17</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>14</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>8</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10">
         <v>8</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10">
         <v>5</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10">
         <v>4</v>
       </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>£50K+</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:17">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>1</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>1</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>4</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>4</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>1</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>6</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>5</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>8</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>7</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>10</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11">
         <v>6</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11">
         <v>5</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11">
         <v>2</v>
       </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:17">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12">
         <v>0</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>1</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>5</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>5</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>10</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>6</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>7</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>6</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>8</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>5</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>15</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>62</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12">
         <v>528</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12">
         <v>292</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12">
         <v>285</v>
+      </c>
+      <c r="Q12">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -555,7 +555,7 @@
         <v>56</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -830,7 +830,7 @@
         <v>70</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1105,7 +1105,7 @@
         <v>282</v>
       </c>
       <c r="Q12" t="n">
-        <v>116</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -552,7 +552,7 @@
         <v>78</v>
       </c>
       <c r="P2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q2" t="n">
         <v>4</v>
@@ -772,7 +772,7 @@
         <v>87</v>
       </c>
       <c r="P6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -827,7 +827,7 @@
         <v>171</v>
       </c>
       <c r="P7" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1105,7 +1105,7 @@
         <v>282</v>
       </c>
       <c r="Q12" t="n">
-        <v>74</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -534,28 +534,28 @@
         <v>356</v>
       </c>
       <c r="J2" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K2" t="n">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="L2" t="n">
         <v>40</v>
       </c>
       <c r="M2" t="n">
-        <v>1553</v>
+        <v>1496</v>
       </c>
       <c r="N2" t="n">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="O2" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="P2" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -598,13 +598,13 @@
         <v>20</v>
       </c>
       <c r="M3" t="n">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="N3" t="n">
         <v>82</v>
       </c>
       <c r="O3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -647,25 +647,25 @@
         <v>169</v>
       </c>
       <c r="K4" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M4" t="n">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="N4" t="n">
         <v>158</v>
       </c>
       <c r="O4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P4" t="n">
         <v>8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -699,19 +699,19 @@
         <v>87</v>
       </c>
       <c r="J5" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K5" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="L5" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="M5" t="n">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="N5" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O5" t="n">
         <v>80</v>
@@ -720,7 +720,7 @@
         <v>13</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -739,7 +739,7 @@
         <v>22</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" t="n">
         <v>26</v>
@@ -757,25 +757,25 @@
         <v>172</v>
       </c>
       <c r="K6" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="L6" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M6" t="n">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="N6" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="O6" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="P6" t="n">
         <v>22</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -797,7 +797,7 @@
         <v>42</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" t="n">
         <v>28</v>
@@ -812,25 +812,25 @@
         <v>254</v>
       </c>
       <c r="K7" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="L7" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M7" t="n">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="N7" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="O7" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="P7" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -867,25 +867,25 @@
         <v>49</v>
       </c>
       <c r="K8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L8" t="n">
         <v>50</v>
       </c>
       <c r="M8" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N8" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -922,19 +922,19 @@
         <v>30</v>
       </c>
       <c r="K9" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L9" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M9" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="N9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P9" t="n">
         <v>33</v>
@@ -977,10 +977,10 @@
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M10" t="n">
         <v>8</v>
@@ -1069,10 +1069,10 @@
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G12" t="n">
         <v>6</v>
@@ -1084,28 +1084,28 @@
         <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="L12" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="M12" t="n">
-        <v>68</v>
+        <v>156</v>
       </c>
       <c r="N12" t="n">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="O12" t="n">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="P12" t="n">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="Q12" t="n">
-        <v>106</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -537,22 +537,22 @@
         <v>394</v>
       </c>
       <c r="K2" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="L2" t="n">
         <v>40</v>
       </c>
       <c r="M2" t="n">
-        <v>1496</v>
+        <v>1553</v>
       </c>
       <c r="N2" t="n">
-        <v>964</v>
+        <v>978</v>
       </c>
       <c r="O2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q2" t="n">
         <v>5</v>
@@ -592,16 +592,16 @@
         <v>132</v>
       </c>
       <c r="K3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M3" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="N3" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O3" t="n">
         <v>17</v>
@@ -647,16 +647,16 @@
         <v>169</v>
       </c>
       <c r="K4" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="M4" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="N4" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="O4" t="n">
         <v>42</v>
@@ -702,19 +702,19 @@
         <v>264</v>
       </c>
       <c r="K5" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="L5" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="M5" t="n">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="N5" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="O5" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P5" t="n">
         <v>13</v>
@@ -757,22 +757,22 @@
         <v>172</v>
       </c>
       <c r="K6" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="L6" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M6" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="N6" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O6" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q6" t="n">
         <v>18</v>
@@ -812,22 +812,22 @@
         <v>254</v>
       </c>
       <c r="K7" t="n">
+        <v>203</v>
+      </c>
+      <c r="L7" t="n">
         <v>199</v>
       </c>
-      <c r="L7" t="n">
-        <v>197</v>
-      </c>
       <c r="M7" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="N7" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="O7" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="P7" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q7" t="n">
         <v>15</v>
@@ -867,7 +867,7 @@
         <v>49</v>
       </c>
       <c r="K8" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L8" t="n">
         <v>50</v>
@@ -922,19 +922,19 @@
         <v>30</v>
       </c>
       <c r="K9" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M9" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P9" t="n">
         <v>33</v>
@@ -977,10 +977,10 @@
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M10" t="n">
         <v>8</v>
@@ -1087,22 +1087,22 @@
         <v>8</v>
       </c>
       <c r="K12" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="M12" t="n">
-        <v>156</v>
+        <v>63</v>
       </c>
       <c r="N12" t="n">
-        <v>563</v>
+        <v>529</v>
       </c>
       <c r="O12" t="n">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="P12" t="n">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="Q12" t="n">
         <v>45</v>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -516,40 +516,40 @@
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E2" t="n">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="F2" t="n">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G2" t="n">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H2" t="n">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="I2" t="n">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="J2" t="n">
-        <v>394</v>
+        <v>362</v>
       </c>
       <c r="K2" t="n">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="L2" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M2" t="n">
-        <v>1553</v>
+        <v>1520</v>
       </c>
       <c r="N2" t="n">
-        <v>978</v>
+        <v>959</v>
       </c>
       <c r="O2" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="P2" t="n">
         <v>54</v>
@@ -568,46 +568,46 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H3" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I3" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J3" t="n">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="K3" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="L3" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="M3" t="n">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="N3" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="O3" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -623,46 +623,46 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>26</v>
+      </c>
+      <c r="G4" t="n">
         <v>18</v>
       </c>
-      <c r="E4" t="n">
-        <v>21</v>
-      </c>
-      <c r="F4" t="n">
-        <v>36</v>
-      </c>
-      <c r="G4" t="n">
-        <v>22</v>
-      </c>
       <c r="H4" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="I4" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="J4" t="n">
-        <v>169</v>
+        <v>130</v>
       </c>
       <c r="K4" t="n">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="L4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="M4" t="n">
-        <v>246</v>
+        <v>182</v>
       </c>
       <c r="N4" t="n">
-        <v>162</v>
+        <v>124</v>
       </c>
       <c r="O4" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="P4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
@@ -675,52 +675,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E5" t="n">
+        <v>42</v>
+      </c>
+      <c r="F5" t="n">
+        <v>34</v>
+      </c>
+      <c r="G5" t="n">
         <v>29</v>
       </c>
-      <c r="F5" t="n">
-        <v>14</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
+        <v>52</v>
+      </c>
+      <c r="I5" t="n">
+        <v>111</v>
+      </c>
+      <c r="J5" t="n">
+        <v>345</v>
+      </c>
+      <c r="K5" t="n">
+        <v>187</v>
+      </c>
+      <c r="L5" t="n">
+        <v>123</v>
+      </c>
+      <c r="M5" t="n">
+        <v>425</v>
+      </c>
+      <c r="N5" t="n">
+        <v>272</v>
+      </c>
+      <c r="O5" t="n">
+        <v>111</v>
+      </c>
+      <c r="P5" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q5" t="n">
         <v>25</v>
-      </c>
-      <c r="H5" t="n">
-        <v>40</v>
-      </c>
-      <c r="I5" t="n">
-        <v>87</v>
-      </c>
-      <c r="J5" t="n">
-        <v>264</v>
-      </c>
-      <c r="K5" t="n">
-        <v>142</v>
-      </c>
-      <c r="L5" t="n">
-        <v>99</v>
-      </c>
-      <c r="M5" t="n">
-        <v>324</v>
-      </c>
-      <c r="N5" t="n">
-        <v>215</v>
-      </c>
-      <c r="O5" t="n">
-        <v>83</v>
-      </c>
-      <c r="P5" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -730,52 +730,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
         <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I6" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="J6" t="n">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="K6" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="L6" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>211</v>
+        <v>251</v>
       </c>
       <c r="N6" t="n">
         <v>151</v>
       </c>
       <c r="O6" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="P6" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="Q6" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -785,52 +785,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H7" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I7" t="n">
         <v>126</v>
       </c>
       <c r="J7" t="n">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K7" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="L7" t="n">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="M7" t="n">
-        <v>327</v>
+        <v>306</v>
       </c>
       <c r="N7" t="n">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="O7" t="n">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="P7" t="n">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -840,49 +840,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
         <v>9</v>
       </c>
-      <c r="E8" t="n">
-        <v>19</v>
-      </c>
-      <c r="F8" t="n">
-        <v>6</v>
-      </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J8" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K8" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="L8" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M8" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="N8" t="n">
+        <v>42</v>
+      </c>
+      <c r="O8" t="n">
         <v>31</v>
       </c>
-      <c r="O8" t="n">
-        <v>30</v>
-      </c>
       <c r="P8" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="Q8" t="n">
         <v>2</v>
@@ -895,52 +895,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J9" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K9" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="L9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M9" t="n">
+        <v>37</v>
+      </c>
+      <c r="N9" t="n">
+        <v>27</v>
+      </c>
+      <c r="O9" t="n">
+        <v>26</v>
+      </c>
+      <c r="P9" t="n">
         <v>34</v>
       </c>
-      <c r="N9" t="n">
-        <v>29</v>
-      </c>
-      <c r="O9" t="n">
-        <v>18</v>
-      </c>
-      <c r="P9" t="n">
-        <v>33</v>
-      </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
         <v>8</v>
@@ -968,13 +968,13 @@
         <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K10" t="n">
         <v>17</v>
@@ -983,16 +983,16 @@
         <v>14</v>
       </c>
       <c r="M10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1005,49 +1005,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
         <v>6</v>
       </c>
-      <c r="J11" t="n">
-        <v>5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>8</v>
-      </c>
       <c r="L11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" t="n">
+        <v>9</v>
+      </c>
+      <c r="N11" t="n">
         <v>7</v>
-      </c>
-      <c r="M11" t="n">
-        <v>10</v>
-      </c>
-      <c r="N11" t="n">
-        <v>6</v>
       </c>
       <c r="O11" t="n">
         <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1066,7 +1066,7 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
         <v>5</v>
@@ -1081,31 +1081,31 @@
         <v>7</v>
       </c>
       <c r="I12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" t="n">
         <v>6</v>
       </c>
-      <c r="J12" t="n">
-        <v>8</v>
-      </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>15</v>
       </c>
       <c r="M12" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="N12" t="n">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="O12" t="n">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="P12" t="n">
-        <v>272</v>
+        <v>204</v>
       </c>
       <c r="Q12" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -720,7 +720,7 @@
         <v>17</v>
       </c>
       <c r="Q5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -775,7 +775,7 @@
         <v>35</v>
       </c>
       <c r="Q6" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -830,7 +830,7 @@
         <v>111</v>
       </c>
       <c r="Q7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -940,7 +940,7 @@
         <v>34</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1105,7 +1105,7 @@
         <v>204</v>
       </c>
       <c r="Q12" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -555,7 +555,7 @@
         <v>54</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -720,7 +720,7 @@
         <v>17</v>
       </c>
       <c r="Q5" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -775,7 +775,7 @@
         <v>35</v>
       </c>
       <c r="Q6" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -830,7 +830,7 @@
         <v>111</v>
       </c>
       <c r="Q7" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8">
@@ -885,7 +885,7 @@
         <v>32</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -940,7 +940,7 @@
         <v>34</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -995,7 +995,7 @@
         <v>12</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1050,7 +1050,7 @@
         <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1105,7 +1105,7 @@
         <v>204</v>
       </c>
       <c r="Q12" t="n">
-        <v>63</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -555,7 +555,7 @@
         <v>54</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -885,7 +885,7 @@
         <v>32</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -940,7 +940,7 @@
         <v>34</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -1050,7 +1050,7 @@
         <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1105,7 +1105,7 @@
         <v>204</v>
       </c>
       <c r="Q12" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -1,40 +1,135 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+  <si>
+    <t>GMV slab</t>
+  </si>
+  <si>
+    <t>2025-07</t>
+  </si>
+  <si>
+    <t>2025-08</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>2025-11</t>
+  </si>
+  <si>
+    <t>2025-12</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+  <si>
+    <t>£0-£50</t>
+  </si>
+  <si>
+    <t>£50-£100</t>
+  </si>
+  <si>
+    <t>£100-£200</t>
+  </si>
+  <si>
+    <t>£200-£500</t>
+  </si>
+  <si>
+    <t>£500-£1K</t>
+  </si>
+  <si>
+    <t>£1K-£5K</t>
+  </si>
+  <si>
+    <t>£5K-£10K</t>
+  </si>
+  <si>
+    <t>£10K-£25K</t>
+  </si>
+  <si>
+    <t>£25K-£50K</t>
+  </si>
+  <si>
+    <t>£50K+</t>
+  </si>
+  <si>
+    <t>No data</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +137,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,707 +454,647 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>GMV slab</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
+    <row r="1" spans="1:17">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="2" spans="1:17">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
         <v>15</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>12</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>241</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>390</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>455</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>291</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>609</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>347</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>362</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>135</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>35</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>1520</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>959</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2">
         <v>80</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2">
         <v>54</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2">
         <v>7</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>£50-£100</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:17">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>17</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>11</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>19</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>17</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>33</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>46</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>116</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>54</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>15</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>164</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>75</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3">
         <v>13</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3">
         <v>2</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3">
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>£100-£200</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:17">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>2</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>15</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>12</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>26</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>18</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>38</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>37</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>130</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>63</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>16</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>182</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>124</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4">
         <v>31</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4">
         <v>7</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4">
         <v>3</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>£200-£500</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:17">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
         <v>9</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>7</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>51</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>42</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>34</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>29</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>52</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>111</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>345</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>187</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>123</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>425</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5">
         <v>272</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5">
         <v>111</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5">
         <v>17</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5">
         <v>52</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>£500-£1K</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:17">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6">
         <v>11</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>6</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>28</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>25</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>26</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>22</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>24</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>69</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>191</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>132</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>100</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>251</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>151</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6">
         <v>86</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6">
         <v>35</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6">
         <v>50</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>£1K-£5K</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:17">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7">
         <v>9</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>5</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>51</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>46</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>34</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>22</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>30</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>126</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>238</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>195</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>173</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>306</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7">
         <v>184</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7">
         <v>168</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7">
         <v>111</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7">
         <v>55</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:17">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8">
         <v>9</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>3</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>13</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>12</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>9</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>11</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>5</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>28</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>57</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>53</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>56</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>64</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8">
         <v>42</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8">
         <v>31</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8">
         <v>32</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8">
         <v>24</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>£10K-£25K</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:17">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
         <v>6</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>2</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>8</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>16</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>6</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>11</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>8</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>33</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>25</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>33</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>34</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>37</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9">
         <v>27</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9">
         <v>26</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9">
         <v>34</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9">
         <v>15</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>£25K-£50K</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:17">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10">
         <v>6</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>0</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>4</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>4</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>8</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>2</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>5</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>15</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>13</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>17</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>14</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>9</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10">
         <v>6</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10">
         <v>7</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10">
         <v>12</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10">
         <v>3</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>£50K+</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:17">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11">
         <v>0</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>1</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>0</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>5</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>2</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>2</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>1</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>5</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>3</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>6</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>6</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>9</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11">
         <v>7</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11">
         <v>5</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11">
         <v>3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11">
         <v>2</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:17">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12">
         <v>0</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>1</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>4</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>5</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>10</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>6</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>7</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>4</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>2</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>15</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>59</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12">
         <v>521</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12">
         <v>289</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12">
         <v>204</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12">
         <v>110</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -720,7 +720,7 @@
         <v>17</v>
       </c>
       <c r="Q5">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -773,7 +773,7 @@
         <v>35</v>
       </c>
       <c r="Q6">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -826,7 +826,7 @@
         <v>111</v>
       </c>
       <c r="Q7">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -879,7 +879,7 @@
         <v>32</v>
       </c>
       <c r="Q8">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -932,7 +932,7 @@
         <v>34</v>
       </c>
       <c r="Q9">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -985,7 +985,7 @@
         <v>12</v>
       </c>
       <c r="Q10">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -1038,7 +1038,7 @@
         <v>3</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1091,7 +1091,7 @@
         <v>204</v>
       </c>
       <c r="Q12">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -555,7 +555,7 @@
         <v>54</v>
       </c>
       <c r="Q2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -665,7 +665,7 @@
         <v>7</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -720,7 +720,7 @@
         <v>17</v>
       </c>
       <c r="Q5" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
@@ -775,7 +775,7 @@
         <v>35</v>
       </c>
       <c r="Q6" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
@@ -830,7 +830,7 @@
         <v>111</v>
       </c>
       <c r="Q7" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -885,7 +885,7 @@
         <v>32</v>
       </c>
       <c r="Q8" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
@@ -940,7 +940,7 @@
         <v>34</v>
       </c>
       <c r="Q9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -1105,7 +1105,7 @@
         <v>204</v>
       </c>
       <c r="Q12" t="n">
-        <v>116</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -555,7 +555,7 @@
         <v>54</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -720,7 +720,7 @@
         <v>17</v>
       </c>
       <c r="Q5" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6">
@@ -775,7 +775,7 @@
         <v>35</v>
       </c>
       <c r="Q6" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7">
@@ -830,7 +830,7 @@
         <v>111</v>
       </c>
       <c r="Q7" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8">
@@ -885,7 +885,7 @@
         <v>32</v>
       </c>
       <c r="Q8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -940,7 +940,7 @@
         <v>34</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -1105,7 +1105,7 @@
         <v>204</v>
       </c>
       <c r="Q12" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -555,7 +555,7 @@
         <v>54</v>
       </c>
       <c r="Q2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -665,7 +665,7 @@
         <v>7</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -720,7 +720,7 @@
         <v>17</v>
       </c>
       <c r="Q5" t="n">
-        <v>89</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6">
@@ -775,7 +775,7 @@
         <v>35</v>
       </c>
       <c r="Q6" t="n">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7">
@@ -818,7 +818,7 @@
         <v>173</v>
       </c>
       <c r="M7" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N7" t="n">
         <v>184</v>
@@ -827,10 +827,10 @@
         <v>168</v>
       </c>
       <c r="P7" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q7" t="n">
-        <v>82</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8">
@@ -885,7 +885,7 @@
         <v>32</v>
       </c>
       <c r="Q8" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9">
@@ -937,10 +937,10 @@
         <v>26</v>
       </c>
       <c r="P9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q9" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -995,7 +995,7 @@
         <v>12</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1050,7 +1050,7 @@
         <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1093,7 +1093,7 @@
         <v>15</v>
       </c>
       <c r="M12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N12" t="n">
         <v>521</v>
@@ -1102,10 +1102,10 @@
         <v>290</v>
       </c>
       <c r="P12" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="Q12" t="n">
-        <v>149</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -546,16 +546,16 @@
         <v>1520</v>
       </c>
       <c r="N2" t="n">
-        <v>959</v>
+        <v>948</v>
       </c>
       <c r="O2" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="P2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -601,10 +601,10 @@
         <v>164</v>
       </c>
       <c r="N3" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="O3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -644,7 +644,7 @@
         <v>37</v>
       </c>
       <c r="J4" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K4" t="n">
         <v>63</v>
@@ -653,10 +653,10 @@
         <v>16</v>
       </c>
       <c r="M4" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N4" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="O4" t="n">
         <v>31</v>
@@ -693,13 +693,13 @@
         <v>29</v>
       </c>
       <c r="H5" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I5" t="n">
         <v>111</v>
       </c>
       <c r="J5" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K5" t="n">
         <v>187</v>
@@ -711,16 +711,16 @@
         <v>425</v>
       </c>
       <c r="N5" t="n">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="O5" t="n">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="P5" t="n">
         <v>17</v>
       </c>
       <c r="Q5" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
         <v>6</v>
@@ -742,13 +742,13 @@
         <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
         <v>22</v>
       </c>
       <c r="H6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I6" t="n">
         <v>69</v>
@@ -763,7 +763,7 @@
         <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N6" t="n">
         <v>151</v>
@@ -775,7 +775,7 @@
         <v>35</v>
       </c>
       <c r="Q6" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7">
@@ -803,7 +803,7 @@
         <v>22</v>
       </c>
       <c r="H7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7" t="n">
         <v>126</v>
@@ -821,16 +821,16 @@
         <v>307</v>
       </c>
       <c r="N7" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O7" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P7" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q7" t="n">
-        <v>167</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8">
@@ -876,16 +876,16 @@
         <v>64</v>
       </c>
       <c r="N8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="O8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P8" t="n">
         <v>32</v>
       </c>
       <c r="Q8" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="O9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P9" t="n">
         <v>35</v>
       </c>
       <c r="Q9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -1050,7 +1050,7 @@
         <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -1072,13 +1072,13 @@
         <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
         <v>4</v>
@@ -1093,19 +1093,19 @@
         <v>15</v>
       </c>
       <c r="M12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="N12" t="n">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="O12" t="n">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="P12" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Q12" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -720,7 +720,7 @@
         <v>17</v>
       </c>
       <c r="Q5" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6">
@@ -775,7 +775,7 @@
         <v>35</v>
       </c>
       <c r="Q6" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7">
@@ -830,7 +830,7 @@
         <v>113</v>
       </c>
       <c r="Q7" t="n">
-        <v>176</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8">
@@ -940,7 +940,7 @@
         <v>35</v>
       </c>
       <c r="Q9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -995,7 +995,7 @@
         <v>12</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -1050,7 +1050,7 @@
         <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -1105,7 +1105,7 @@
         <v>200</v>
       </c>
       <c r="Q12" t="n">
-        <v>213</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -555,7 +555,7 @@
         <v>55</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -610,7 +610,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -665,7 +665,7 @@
         <v>7</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -720,7 +720,7 @@
         <v>17</v>
       </c>
       <c r="Q5" t="n">
-        <v>143</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6">
@@ -775,7 +775,7 @@
         <v>35</v>
       </c>
       <c r="Q6" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7">
@@ -824,13 +824,13 @@
         <v>185</v>
       </c>
       <c r="O7" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P7" t="n">
         <v>113</v>
       </c>
       <c r="Q7" t="n">
-        <v>184</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8">
@@ -882,10 +882,10 @@
         <v>25</v>
       </c>
       <c r="P8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q8" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
@@ -937,10 +937,10 @@
         <v>25</v>
       </c>
       <c r="P9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q9" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -995,7 +995,7 @@
         <v>12</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -1099,13 +1099,13 @@
         <v>539</v>
       </c>
       <c r="O12" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P12" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q12" t="n">
-        <v>251</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -561,7 +561,7 @@
         <v>56</v>
       </c>
       <c r="Q2">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -614,7 +614,7 @@
         <v>2</v>
       </c>
       <c r="Q3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -720,7 +720,7 @@
         <v>17</v>
       </c>
       <c r="Q5">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -773,7 +773,7 @@
         <v>35</v>
       </c>
       <c r="Q6">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -826,7 +826,7 @@
         <v>113</v>
       </c>
       <c r="Q7">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -879,7 +879,7 @@
         <v>34</v>
       </c>
       <c r="Q8">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -932,7 +932,7 @@
         <v>34</v>
       </c>
       <c r="Q9">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -1038,7 +1038,7 @@
         <v>3</v>
       </c>
       <c r="Q11">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1091,7 +1091,7 @@
         <v>198</v>
       </c>
       <c r="Q12">
-        <v>294</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -1,40 +1,135 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+  <si>
+    <t>GMV slab</t>
+  </si>
+  <si>
+    <t>2025-07</t>
+  </si>
+  <si>
+    <t>2025-08</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>2025-11</t>
+  </si>
+  <si>
+    <t>2025-12</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+  <si>
+    <t>£0-£50</t>
+  </si>
+  <si>
+    <t>£50-£100</t>
+  </si>
+  <si>
+    <t>£100-£200</t>
+  </si>
+  <si>
+    <t>£200-£500</t>
+  </si>
+  <si>
+    <t>£500-£1K</t>
+  </si>
+  <si>
+    <t>£1K-£5K</t>
+  </si>
+  <si>
+    <t>£5K-£10K</t>
+  </si>
+  <si>
+    <t>£10K-£25K</t>
+  </si>
+  <si>
+    <t>£25K-£50K</t>
+  </si>
+  <si>
+    <t>£50K+</t>
+  </si>
+  <si>
+    <t>No data</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +137,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,707 +454,647 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>GMV slab</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
+    <row r="1" spans="1:17">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="2" spans="1:17">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
         <v>15</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>12</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>241</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>390</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>455</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>291</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>609</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>347</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>362</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>135</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>35</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>1520</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>948</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2">
         <v>63</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2">
         <v>56</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2">
         <v>18</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>£50-£100</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:17">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>17</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>11</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>19</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>17</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>33</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>46</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>116</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>54</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>15</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>164</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>78</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3">
         <v>11</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3">
         <v>2</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3">
         <v>4</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>£100-£200</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:17">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>2</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>15</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>12</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>26</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>18</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>38</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>37</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>131</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>63</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>16</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>181</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>127</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4">
         <v>31</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4">
         <v>7</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4">
         <v>8</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>£200-£500</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:17">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
         <v>9</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>7</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>51</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>42</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>34</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>29</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>51</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>111</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>344</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>187</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>123</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>425</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5">
         <v>260</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5">
         <v>102</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5">
         <v>17</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5">
         <v>161</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>£500-£1K</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:17">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6">
         <v>10</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>6</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>28</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>25</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>25</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>22</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>23</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>69</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>191</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>132</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>100</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>250</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>151</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6">
         <v>86</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6">
         <v>35</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6">
         <v>134</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>£1K-£5K</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:17">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7">
         <v>9</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>5</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>51</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>46</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>34</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>22</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>31</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>126</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>238</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>195</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>173</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>307</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7">
         <v>185</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7">
         <v>167</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7">
         <v>113</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7">
         <v>223</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:17">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8">
         <v>9</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>3</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>13</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>12</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>9</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>11</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>5</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>28</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>57</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>53</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>56</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>64</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8">
         <v>40</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8">
         <v>25</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8">
         <v>34</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8">
         <v>62</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>£10K-£25K</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:17">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
         <v>6</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>2</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>8</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>16</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>6</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>11</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>8</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>33</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>25</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>33</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>34</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>37</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9">
         <v>27</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9">
         <v>25</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9">
         <v>34</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9">
         <v>48</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>£25K-£50K</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:17">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10">
         <v>6</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>0</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>4</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>4</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>8</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>2</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>5</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>15</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>13</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>17</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>14</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>9</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10">
         <v>6</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10">
         <v>7</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10">
         <v>12</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10">
         <v>8</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>£50K+</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:17">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11">
         <v>0</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>1</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>0</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>5</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>2</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>2</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>1</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>5</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>3</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>6</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>6</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>9</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11">
         <v>7</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11">
         <v>5</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11">
         <v>3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11">
         <v>7</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:17">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>1</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>4</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>5</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>11</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>6</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>8</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>4</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>2</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>15</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>60</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12">
         <v>539</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12">
         <v>325</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12">
         <v>198</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12">
         <v>338</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -531,37 +531,37 @@
         <v>455</v>
       </c>
       <c r="G2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="I2">
         <v>347</v>
       </c>
       <c r="J2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="K2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M2">
-        <v>1520</v>
+        <v>1511</v>
       </c>
       <c r="N2">
-        <v>948</v>
+        <v>854</v>
       </c>
       <c r="O2">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="P2">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="Q2">
-        <v>18</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -575,7 +575,7 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3">
         <v>11</v>
@@ -590,10 +590,10 @@
         <v>33</v>
       </c>
       <c r="I3">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J3">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K3">
         <v>54</v>
@@ -602,19 +602,19 @@
         <v>15</v>
       </c>
       <c r="M3">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N3">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="O3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P3">
         <v>2</v>
       </c>
       <c r="Q3">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -637,37 +637,37 @@
         <v>26</v>
       </c>
       <c r="G4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4">
+        <v>39</v>
+      </c>
+      <c r="I4">
         <v>38</v>
       </c>
-      <c r="I4">
-        <v>37</v>
-      </c>
       <c r="J4">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="K4">
         <v>63</v>
       </c>
       <c r="L4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M4">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N4">
         <v>127</v>
       </c>
       <c r="O4">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="P4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -681,28 +681,28 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H5">
         <v>51</v>
       </c>
       <c r="I5">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J5">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="K5">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L5">
         <v>123</v>
@@ -711,16 +711,16 @@
         <v>425</v>
       </c>
       <c r="N5">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O5">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="P5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q5">
-        <v>161</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -737,43 +737,43 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F6">
         <v>25</v>
       </c>
       <c r="G6">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H6">
         <v>23</v>
       </c>
       <c r="I6">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J6">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K6">
         <v>132</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="M6">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="N6">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="O6">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q6">
-        <v>134</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -790,43 +790,43 @@
         <v>51</v>
       </c>
       <c r="E7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H7">
         <v>31</v>
       </c>
       <c r="I7">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J7">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K7">
         <v>195</v>
       </c>
       <c r="L7">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="M7">
         <v>307</v>
       </c>
       <c r="N7">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P7">
         <v>113</v>
       </c>
       <c r="Q7">
-        <v>223</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -843,13 +843,13 @@
         <v>13</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8">
         <v>9</v>
       </c>
       <c r="G8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H8">
         <v>5</v>
@@ -861,25 +861,25 @@
         <v>57</v>
       </c>
       <c r="K8">
+        <v>56</v>
+      </c>
+      <c r="L8">
         <v>53</v>
       </c>
-      <c r="L8">
-        <v>56</v>
-      </c>
       <c r="M8">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N8">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="O8">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q8">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -902,7 +902,7 @@
         <v>6</v>
       </c>
       <c r="G9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H9">
         <v>8</v>
@@ -914,16 +914,16 @@
         <v>25</v>
       </c>
       <c r="K9">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L9">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M9">
         <v>37</v>
       </c>
       <c r="N9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O9">
         <v>25</v>
@@ -932,7 +932,7 @@
         <v>34</v>
       </c>
       <c r="Q9">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -949,7 +949,7 @@
         <v>4</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10">
         <v>8</v>
@@ -964,7 +964,7 @@
         <v>15</v>
       </c>
       <c r="J10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K10">
         <v>17</v>
@@ -985,7 +985,7 @@
         <v>12</v>
       </c>
       <c r="Q10">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11">
         <v>2</v>
@@ -1017,7 +1017,7 @@
         <v>5</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11">
         <v>6</v>
@@ -1038,7 +1038,7 @@
         <v>3</v>
       </c>
       <c r="Q11">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1061,7 +1061,7 @@
         <v>11</v>
       </c>
       <c r="G12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H12">
         <v>8</v>
@@ -1073,25 +1073,25 @@
         <v>6</v>
       </c>
       <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
         <v>2</v>
       </c>
-      <c r="L12">
-        <v>15</v>
-      </c>
       <c r="M12">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="N12">
-        <v>539</v>
+        <v>32</v>
       </c>
       <c r="O12">
-        <v>325</v>
+        <v>29</v>
       </c>
       <c r="P12">
-        <v>198</v>
+        <v>28</v>
       </c>
       <c r="Q12">
-        <v>338</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -525,34 +525,34 @@
         <v>241</v>
       </c>
       <c r="E2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="F2">
-        <v>455</v>
+        <v>505</v>
       </c>
       <c r="G2">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="H2">
-        <v>608</v>
+        <v>666</v>
       </c>
       <c r="I2">
-        <v>347</v>
+        <v>439</v>
       </c>
       <c r="J2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="K2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L2">
         <v>32</v>
       </c>
       <c r="M2">
-        <v>1511</v>
+        <v>1504</v>
       </c>
       <c r="N2">
-        <v>854</v>
+        <v>846</v>
       </c>
       <c r="O2">
         <v>37</v>
@@ -561,7 +561,7 @@
         <v>46</v>
       </c>
       <c r="Q2">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -578,37 +578,37 @@
         <v>18</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H3">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="I3">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="J3">
         <v>117</v>
       </c>
       <c r="K3">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L3">
         <v>15</v>
       </c>
       <c r="M3">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="N3">
         <v>73</v>
       </c>
       <c r="O3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P3">
         <v>2</v>
@@ -631,31 +631,31 @@
         <v>15</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H4">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="I4">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="J4">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K4">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L4">
         <v>17</v>
       </c>
       <c r="M4">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N4">
         <v>127</v>
@@ -667,7 +667,7 @@
         <v>8</v>
       </c>
       <c r="Q4">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -684,43 +684,43 @@
         <v>50</v>
       </c>
       <c r="E5">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H5">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="I5">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="J5">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="K5">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="L5">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M5">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="N5">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="O5">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="P5">
         <v>16</v>
       </c>
       <c r="Q5">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -737,43 +737,43 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F6">
+        <v>32</v>
+      </c>
+      <c r="G6">
+        <v>31</v>
+      </c>
+      <c r="H6">
         <v>25</v>
       </c>
-      <c r="G6">
-        <v>19</v>
-      </c>
-      <c r="H6">
-        <v>23</v>
-      </c>
       <c r="I6">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="J6">
         <v>186</v>
       </c>
       <c r="K6">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="L6">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M6">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="N6">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="O6">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P6">
         <v>34</v>
       </c>
       <c r="Q6">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -790,43 +790,43 @@
         <v>51</v>
       </c>
       <c r="E7">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F7">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G7">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H7">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="I7">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="J7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="K7">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="L7">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M7">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="N7">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O7">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="P7">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q7">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -840,46 +840,46 @@
         <v>3</v>
       </c>
       <c r="D8">
+        <v>14</v>
+      </c>
+      <c r="E8">
+        <v>14</v>
+      </c>
+      <c r="F8">
+        <v>11</v>
+      </c>
+      <c r="G8">
         <v>13</v>
-      </c>
-      <c r="E8">
-        <v>11</v>
-      </c>
-      <c r="F8">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>12</v>
       </c>
       <c r="H8">
         <v>5</v>
       </c>
       <c r="I8">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J8">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K8">
         <v>56</v>
       </c>
       <c r="L8">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M8">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N8">
         <v>44</v>
       </c>
       <c r="O8">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P8">
         <v>35</v>
       </c>
       <c r="Q8">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -896,22 +896,22 @@
         <v>8</v>
       </c>
       <c r="E9">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G9">
+        <v>11</v>
+      </c>
+      <c r="H9">
         <v>10</v>
       </c>
-      <c r="H9">
-        <v>8</v>
-      </c>
       <c r="I9">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K9">
         <v>32</v>
@@ -920,7 +920,7 @@
         <v>36</v>
       </c>
       <c r="M9">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N9">
         <v>26</v>
@@ -932,7 +932,7 @@
         <v>34</v>
       </c>
       <c r="Q9">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -955,22 +955,22 @@
         <v>8</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I10">
+        <v>18</v>
+      </c>
+      <c r="J10">
+        <v>11</v>
+      </c>
+      <c r="K10">
         <v>15</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>12</v>
-      </c>
-      <c r="K10">
-        <v>17</v>
-      </c>
-      <c r="L10">
-        <v>14</v>
       </c>
       <c r="M10">
         <v>9</v>
@@ -1002,10 +1002,10 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1032,7 +1032,7 @@
         <v>7</v>
       </c>
       <c r="O11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P11">
         <v>3</v>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -552,10 +552,10 @@
         <v>1504</v>
       </c>
       <c r="N2">
-        <v>846</v>
+        <v>853</v>
       </c>
       <c r="O2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="P2">
         <v>46</v>
@@ -605,10 +605,10 @@
         <v>161</v>
       </c>
       <c r="N3">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P3">
         <v>2</v>
@@ -634,13 +634,13 @@
         <v>13</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4">
         <v>24</v>
       </c>
       <c r="H4">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I4">
         <v>52</v>
@@ -658,10 +658,10 @@
         <v>181</v>
       </c>
       <c r="N4">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O4">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="P4">
         <v>8</v>
@@ -711,10 +711,10 @@
         <v>417</v>
       </c>
       <c r="N5">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O5">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="P5">
         <v>16</v>
@@ -773,7 +773,7 @@
         <v>34</v>
       </c>
       <c r="Q6">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -820,13 +820,13 @@
         <v>181</v>
       </c>
       <c r="O7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="P7">
         <v>111</v>
       </c>
       <c r="Q7">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -1058,13 +1058,13 @@
         <v>5</v>
       </c>
       <c r="F12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>5</v>
       </c>
       <c r="H12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I12">
         <v>4</v>
@@ -1082,16 +1082,16 @@
         <v>18</v>
       </c>
       <c r="N12">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="O12">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>28</v>
       </c>
       <c r="Q12">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -561,7 +561,7 @@
         <v>46</v>
       </c>
       <c r="Q2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -720,7 +720,7 @@
         <v>16</v>
       </c>
       <c r="Q5">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -773,7 +773,7 @@
         <v>34</v>
       </c>
       <c r="Q6">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -826,7 +826,7 @@
         <v>111</v>
       </c>
       <c r="Q7">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -1091,7 +1091,7 @@
         <v>28</v>
       </c>
       <c r="Q12">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -1,40 +1,135 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+  <si>
+    <t>GMV slab</t>
+  </si>
+  <si>
+    <t>2025-07</t>
+  </si>
+  <si>
+    <t>2025-08</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>2025-11</t>
+  </si>
+  <si>
+    <t>2025-12</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+  <si>
+    <t>£0-£50</t>
+  </si>
+  <si>
+    <t>£50-£100</t>
+  </si>
+  <si>
+    <t>£100-£200</t>
+  </si>
+  <si>
+    <t>£200-£500</t>
+  </si>
+  <si>
+    <t>£500-£1K</t>
+  </si>
+  <si>
+    <t>£1K-£5K</t>
+  </si>
+  <si>
+    <t>£5K-£10K</t>
+  </si>
+  <si>
+    <t>£10K-£25K</t>
+  </si>
+  <si>
+    <t>£25K-£50K</t>
+  </si>
+  <si>
+    <t>£50K+</t>
+  </si>
+  <si>
+    <t>No data</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +137,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,707 +454,647 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>GMV slab</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
+    <row r="1" spans="1:17">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="2" spans="1:17">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
         <v>15</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>12</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>241</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>399</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>505</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>307</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>666</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>439</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>368</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>130</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>32</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>1504</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>853</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2">
         <v>45</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2">
         <v>46</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2">
         <v>37</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>£50-£100</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:17">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>18</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>12</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>26</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>24</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>43</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>59</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>117</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>52</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>15</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>161</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>74</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3">
         <v>10</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3">
         <v>2</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3">
         <v>12</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>£100-£200</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:17">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>2</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>15</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>13</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>32</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>24</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>49</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>52</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>133</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>61</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>17</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>181</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>129</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4">
         <v>34</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4">
         <v>8</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4">
         <v>24</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>£200-£500</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:17">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
         <v>9</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>7</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>50</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>50</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>38</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>38</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>65</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>128</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>350</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>180</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>120</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>417</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5">
         <v>254</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5">
         <v>99</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5">
         <v>16</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5">
         <v>187</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>£500-£1K</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:17">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6">
         <v>10</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>6</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>28</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>29</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>32</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>31</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>25</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>79</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>186</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>125</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>93</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>244</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>144</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6">
         <v>82</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6">
         <v>34</v>
       </c>
-      <c r="Q6" t="n">
-        <v>161</v>
+      <c r="Q6">
+        <v>164</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>£1K-£5K</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:17">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7">
         <v>9</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>5</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>51</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>53</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>45</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>31</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>46</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>144</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>246</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>182</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>176</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>299</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7">
         <v>181</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7">
         <v>166</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7">
         <v>111</v>
       </c>
-      <c r="Q7" t="n">
-        <v>290</v>
+      <c r="Q7">
+        <v>293</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:17">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8">
         <v>9</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>3</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>14</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>14</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>11</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>13</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>5</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>33</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>55</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>56</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>51</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>62</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8">
         <v>44</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8">
         <v>25</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8">
         <v>35</v>
       </c>
-      <c r="Q8" t="n">
-        <v>70</v>
+      <c r="Q8">
+        <v>71</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>£10K-£25K</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:17">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
         <v>6</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>2</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>8</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>18</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>7</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>11</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>10</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>36</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>24</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>32</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>36</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>33</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9">
         <v>26</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9">
         <v>25</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9">
         <v>34</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9">
         <v>51</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>£25K-£50K</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:17">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10">
         <v>6</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>0</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>4</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>3</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>8</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>5</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>7</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>18</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>11</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>15</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>12</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>9</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10">
         <v>6</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10">
         <v>7</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10">
         <v>12</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10">
         <v>10</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>£50K+</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:17">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11">
         <v>0</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>1</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>0</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>9</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>1</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>2</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>1</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>5</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>4</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>6</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>6</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>9</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11">
         <v>7</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11">
         <v>4</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11">
         <v>3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11">
         <v>6</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:17">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>1</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>4</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>5</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>10</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>5</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>7</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>4</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>2</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>18</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12">
         <v>21</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12">
         <v>10</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12">
         <v>28</v>
       </c>
-      <c r="Q12" t="n">
-        <v>86</v>
+      <c r="Q12">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -561,7 +561,7 @@
         <v>46</v>
       </c>
       <c r="Q2">
-        <v>37</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -667,7 +667,7 @@
         <v>8</v>
       </c>
       <c r="Q4">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -720,7 +720,7 @@
         <v>16</v>
       </c>
       <c r="Q5">
-        <v>187</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -773,7 +773,7 @@
         <v>34</v>
       </c>
       <c r="Q6">
-        <v>164</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -826,7 +826,7 @@
         <v>111</v>
       </c>
       <c r="Q7">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -1091,7 +1091,7 @@
         <v>28</v>
       </c>
       <c r="Q12">
-        <v>79</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -720,7 +720,7 @@
         <v>16</v>
       </c>
       <c r="Q5">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -826,7 +826,7 @@
         <v>111</v>
       </c>
       <c r="Q7">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -1091,7 +1091,7 @@
         <v>26</v>
       </c>
       <c r="Q12">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -1,40 +1,135 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+  <si>
+    <t>GMV slab</t>
+  </si>
+  <si>
+    <t>2025-07</t>
+  </si>
+  <si>
+    <t>2025-08</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>2025-11</t>
+  </si>
+  <si>
+    <t>2025-12</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+  <si>
+    <t>£0-£50</t>
+  </si>
+  <si>
+    <t>£50-£100</t>
+  </si>
+  <si>
+    <t>£100-£200</t>
+  </si>
+  <si>
+    <t>£200-£500</t>
+  </si>
+  <si>
+    <t>£500-£1K</t>
+  </si>
+  <si>
+    <t>£1K-£5K</t>
+  </si>
+  <si>
+    <t>£5K-£10K</t>
+  </si>
+  <si>
+    <t>£10K-£25K</t>
+  </si>
+  <si>
+    <t>£25K-£50K</t>
+  </si>
+  <si>
+    <t>£50K+</t>
+  </si>
+  <si>
+    <t>No data</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +137,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,707 +454,647 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>GMV slab</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
+    <row r="1" spans="1:17">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="2" spans="1:17">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
         <v>15</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>12</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>241</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>399</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>505</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>306</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>667</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>439</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>370</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>130</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>32</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>1505</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>852</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2">
         <v>44</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2">
         <v>48</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2">
         <v>74</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>£50-£100</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:17">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>18</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>12</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>26</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>24</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>43</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>59</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>119</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>52</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>16</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>159</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>75</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3">
         <v>11</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3">
         <v>2</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3">
         <v>20</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>£100-£200</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:17">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>2</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>15</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>14</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>32</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>25</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>48</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>52</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>131</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>60</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>17</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>183</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>129</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4">
         <v>34</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4">
         <v>8</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4">
         <v>36</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>£200-£500</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:17">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
         <v>9</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>7</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>50</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>49</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>38</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>38</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>65</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>129</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>347</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>181</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>119</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>416</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5">
         <v>253</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5">
         <v>98</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5">
         <v>16</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5">
         <v>217</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>£500-£1K</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:17">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6">
         <v>10</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>6</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>28</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>28</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>31</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>31</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>25</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>76</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>186</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>126</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>91</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>242</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>142</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6">
         <v>82</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6">
         <v>34</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6">
         <v>199</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>£1K-£5K</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:17">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7">
         <v>9</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>5</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>50</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>54</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>46</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>31</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>46</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>146</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>247</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>178</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>177</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>300</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7">
         <v>185</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7">
         <v>167</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7">
         <v>111</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7">
         <v>385</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:17">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8">
         <v>9</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>3</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>15</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>14</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>11</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>12</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>5</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>33</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>54</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>58</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>52</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>62</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8">
         <v>43</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8">
         <v>25</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8">
         <v>35</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8">
         <v>76</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>£10K-£25K</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:17">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
         <v>6</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>2</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>8</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>18</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>7</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>12</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>10</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>36</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>25</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>33</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>36</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>34</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9">
         <v>26</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9">
         <v>25</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9">
         <v>34</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9">
         <v>62</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>£25K-£50K</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:17">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10">
         <v>6</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>0</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>4</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>3</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>8</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>5</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>7</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>18</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>11</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>15</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>12</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>9</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10">
         <v>6</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10">
         <v>7</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10">
         <v>12</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10">
         <v>11</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>£50K+</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:17">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11">
         <v>0</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>1</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>0</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>9</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>1</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>2</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>1</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>5</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>4</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>6</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>6</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>9</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11">
         <v>7</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11">
         <v>4</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11">
         <v>3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11">
         <v>7</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:17">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>1</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>4</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>5</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>10</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>5</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>7</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>4</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>2</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>18</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12">
         <v>21</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12">
         <v>10</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12">
         <v>26</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -561,7 +561,7 @@
         <v>48</v>
       </c>
       <c r="Q2">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -667,7 +667,7 @@
         <v>8</v>
       </c>
       <c r="Q4">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -773,7 +773,7 @@
         <v>34</v>
       </c>
       <c r="Q6">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -826,7 +826,7 @@
         <v>111</v>
       </c>
       <c r="Q7">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -1091,7 +1091,7 @@
         <v>26</v>
       </c>
       <c r="Q12">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -720,7 +720,7 @@
         <v>16</v>
       </c>
       <c r="Q5">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -773,7 +773,7 @@
         <v>33</v>
       </c>
       <c r="Q6">
-        <v>213</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -826,7 +826,7 @@
         <v>111</v>
       </c>
       <c r="Q7">
-        <v>413</v>
+        <v>464</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -879,7 +879,7 @@
         <v>35</v>
       </c>
       <c r="Q8">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -932,7 +932,7 @@
         <v>34</v>
       </c>
       <c r="Q9">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -1091,7 +1091,7 @@
         <v>26</v>
       </c>
       <c r="Q12">
-        <v>26</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
